--- a/capar_Ex3A_tables.xlsx
+++ b/capar_Ex3A_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cdb2fca04eb2fdb3/Documents/DATA_Labs/W2_Workshop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{2A4753A9-2FBD-406C-AB5D-C486239E0F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB3FFEDA-8110-4CEC-A9DE-3D38D41A78D2}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="8_{2A4753A9-2FBD-406C-AB5D-C486239E0F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDDD62AB-FE3E-4B4B-93D1-5DC8175B04DB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2E7804AA-AA6E-4D44-A495-9D0E67048C03}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{2E7804AA-AA6E-4D44-A495-9D0E67048C03}"/>
   </bookViews>
   <sheets>
     <sheet name="clients" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>client_id</t>
   </si>
@@ -100,16 +100,60 @@
   </si>
   <si>
     <t>walk_dog_id</t>
+  </si>
+  <si>
+    <t>Winnie</t>
+  </si>
+  <si>
+    <t>Chan</t>
+  </si>
+  <si>
+    <t>winniechan@gmail.com</t>
+  </si>
+  <si>
+    <t>396 Sierra Vista Ave</t>
+  </si>
+  <si>
+    <t>Mousse</t>
+  </si>
+  <si>
+    <t>Golden</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>So excited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meric </t>
+  </si>
+  <si>
+    <t>Capar</t>
+  </si>
+  <si>
+    <t>mericcaparrr@gmail.com</t>
+  </si>
+  <si>
+    <t>10.22.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -144,15 +188,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -166,6 +214,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,8 +537,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F451B262-210E-49C7-8982-ADB55EF510E7}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -508,14 +563,37 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>1112223344</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{568CF8C6-B52D-4314-8491-9CAFABC07BEA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC96E866-BF00-4A23-A167-FCA78A3FDF7F}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -541,6 +619,29 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -548,8 +649,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A9C56A9-CCB8-4B84-8B2D-A8712ACE5516}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -568,14 +672,34 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <v>2182608162</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{BD8F5D8B-D4E5-40A7-BCDD-BFD545D68300}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE3FEE13-C9E3-477B-84FE-30C7F77E4D3A}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -598,6 +722,26 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -605,7 +749,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC36BF-7EF6-4F53-88E0-D6F7AE5E0CCC}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -619,6 +763,17 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
